--- a/hojas_de_datos/costes.xlsx
+++ b/hojas_de_datos/costes.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EXT10348\Downloads\WinPython 3.12.10\WPy64-31241\PROYECTOS PYPSA\Dispatching-Project-in-PypSA\hojas_de_datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F4DCD87-CC40-4A30-A072-12FE45964B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7096D91-4609-4AC4-A9AC-A1A5DE5C0DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB02F813-0E5F-4AB1-B800-99DF3CF8E208}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AB02F813-0E5F-4AB1-B800-99DF3CF8E208}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="capital costs" sheetId="1" r:id="rId1"/>
+    <sheet name="marginal costs...." sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>CAPITAL COSTS</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>Links</t>
   </si>
@@ -76,13 +73,73 @@
   </si>
   <si>
     <t>Gas turbine, combined cycle - extraction - natural gas - large</t>
+  </si>
+  <si>
+    <t>Storage Unit</t>
+  </si>
+  <si>
+    <t>h2 store</t>
+  </si>
+  <si>
+    <t>H2 Storage cavern. Capital cost (eur/MWh)</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>Utility-scale Battery Storage - 60 MW - 240 MWh</t>
+  </si>
+  <si>
+    <t>Generator</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t>Onshore Wind</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>Utility-scale PV ground mounted single axis tracking</t>
+  </si>
+  <si>
+    <t>Biomasa</t>
+  </si>
+  <si>
+    <t>Doc: tecnology data for el and dh. Hoja 09a wood chips medium financial data 2050</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>no se añade pq no es extendable</t>
+  </si>
+  <si>
+    <t>doc: tecnology data for el and dh. Hoja 06:financial data-2050</t>
+  </si>
+  <si>
+    <t>CAPITAL COST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuclear </t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,8 +147,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -100,12 +182,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -113,13 +207,70 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -135,55 +286,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>625475</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>77245</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33BEC8AD-4203-70A1-4DCC-962809AC69E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="247650" y="247650"/>
-          <a:ext cx="9055100" cy="4353970"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -503,126 +605,355 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6DDA418-4FB4-49CC-9C88-8C6D046CABAE}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="17.36328125" customWidth="1"/>
-    <col min="4" max="4" width="52.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="1"/>
+    <col min="2" max="2" width="11.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="71.54296875" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.54296875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="17">
+        <v>1360572</v>
+      </c>
+      <c r="F4" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G4" s="17">
+        <v>30</v>
+      </c>
+      <c r="H4" s="17">
+        <v>19574</v>
+      </c>
+      <c r="I4" s="18">
+        <f>(E4*(F4*((1+F4)^G4))/(((1+F4)^G4)-1))+H4</f>
+        <v>97303.477798362073</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="11"/>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="17">
+        <v>465911</v>
+      </c>
+      <c r="F5" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G5" s="17">
+        <v>30</v>
+      </c>
+      <c r="H5" s="17">
+        <v>11525</v>
+      </c>
+      <c r="I5" s="18">
+        <f t="shared" ref="I5:I8" si="0">(E5*(F5*((1+F5)^G5))/(((1+F5)^G5)-1))+H5</f>
+        <v>38142.495237674055</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="11"/>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3402792.6979999999</v>
+      </c>
+      <c r="F6" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G6" s="17">
+        <v>30</v>
+      </c>
+      <c r="H6" s="17">
+        <v>137175.07999999999</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" si="0"/>
+        <v>331576.62543208263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="11"/>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="17">
+        <v>903866.81</v>
+      </c>
+      <c r="F7" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G7" s="17">
+        <v>30</v>
+      </c>
+      <c r="H7" s="17">
+        <v>9038.6681000000008</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
+        <v>60676.578582187896</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="11"/>
+      <c r="C8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="22">
+        <v>5000000</v>
+      </c>
+      <c r="F8" s="24">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G8" s="22">
+        <v>30</v>
+      </c>
+      <c r="H8" s="22">
+        <f>0.02*E8</f>
+        <v>100000</v>
+      </c>
+      <c r="I8" s="23">
+        <f t="shared" si="0"/>
+        <v>385649.99793602276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="12"/>
+      <c r="C9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="10" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E29" t="s">
-        <v>4</v>
-      </c>
-      <c r="F29" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" t="s">
-        <v>6</v>
-      </c>
-      <c r="H29" t="s">
-        <v>7</v>
-      </c>
-      <c r="I29" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G10" s="17">
+        <v>30</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="11"/>
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G11" s="17">
+        <v>30</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B12" s="11"/>
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G30">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C31" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="C32" t="s">
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="17">
+        <v>1145831</v>
+      </c>
+      <c r="F12" s="13">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G12" s="17">
+        <v>30</v>
+      </c>
+      <c r="H12" s="17">
+        <v>45833</v>
+      </c>
+      <c r="I12" s="17">
+        <f>(E12*(F12*((1+F12)^G12))/(((1+F12)^G12)-1))+H12</f>
+        <v>111294.32455700618</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="12"/>
+      <c r="C13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E32">
-        <v>1145831</v>
-      </c>
-      <c r="F32">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G32">
-        <v>30</v>
-      </c>
-      <c r="H32">
-        <v>45833</v>
-      </c>
-      <c r="I32">
-        <f>(E32*(F32*((1+F32)^G32))/(((1+F32)^G32)-1))+H32</f>
-        <v>111294.32455700618</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E13" s="20">
+        <v>1062583</v>
+      </c>
+      <c r="F13" s="15">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G13" s="20">
+        <v>30</v>
+      </c>
+      <c r="H13" s="20">
+        <v>35072</v>
+      </c>
+      <c r="I13" s="20">
+        <f>(E13*(F13*((1+F13)^G13))/(((1+F13)^G13)-1))+H13</f>
+        <v>95777.366351370569</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E33">
-        <v>1062583</v>
-      </c>
-      <c r="F33">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G33">
-        <v>30</v>
-      </c>
-      <c r="H33">
-        <v>35072</v>
-      </c>
-      <c r="I33">
-        <f>(E33*(F33*((1+F33)^G33))/(((1+F33)^G33)-1))+H33</f>
-        <v>95777.366351370569</v>
-      </c>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="F34">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G34">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="F35">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G35">
-        <v>30</v>
+      <c r="C14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="21">
+        <v>1962</v>
+      </c>
+      <c r="F14" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G14" s="21">
+        <v>30</v>
+      </c>
+      <c r="H14" s="21">
+        <v>42</v>
+      </c>
+      <c r="I14" s="21">
+        <f>(E14*(F14*((1+F14)^G14))/(((1+F14)^G14)-1))+H14</f>
+        <v>154.08905919009533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="12"/>
+      <c r="C15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="20">
+        <v>1288686</v>
+      </c>
+      <c r="F15" s="15">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G15" s="20">
+        <v>30</v>
+      </c>
+      <c r="H15" s="20">
+        <v>28490</v>
+      </c>
+      <c r="I15" s="20">
+        <f>(E15*(F15*((1+F15)^G15))/(((1+F15)^G15)-1))+H15</f>
+        <v>102112.63064803628</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="B14:B15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA76F73-5240-4C94-8D82-BAB43D2E0110}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>